--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92568143471</v>
+        <v>46157.93097586072</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097586072</v>
+        <v>46157.93172582616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172582616</v>
+        <v>46157.93399914369</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93399914369</v>
+        <v>46157.93717851298</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717851298</v>
+        <v>46158.28216211223</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28216211223</v>
+        <v>46158.29681126031</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29681126031</v>
+        <v>46158.29814546787</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814546787</v>
+        <v>46158.33387278498</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33387278498</v>
+        <v>46158.36856998001</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Рег ру/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36856998001</v>
+        <v>46158.37287722967</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
